--- a/resultados/rodada03/previa_multiplicadores_v02.xlsx
+++ b/resultados/rodada03/previa_multiplicadores_v02.xlsx
@@ -553,16 +553,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.564386275644761</v>
+        <v>1.564381298281562</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>26.70448449076228</v>
+        <v>26.70307103650656</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26.70448449076228</v>
+        <v>26.70307103650656</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1.543236986542696</v>
@@ -587,16 +587,16 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.564386275644761</v>
+        <v>1.564381298281562</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>26.7044844907623</v>
+        <v>26.70307103650658</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>26.7044844907623</v>
+        <v>26.70307103650658</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1.543236986542697</v>
@@ -621,16 +621,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.513767763912943</v>
+        <v>1.513762541062462</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>25.46265178227029</v>
+        <v>25.46114961428917</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.46265178227029</v>
+        <v>25.46114961428917</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1.492549676898408</v>
@@ -655,16 +655,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.625658601946222</v>
+        <v>1.625654969936375</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>42.05800757683821</v>
+        <v>42.05724347505497</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.2348292186667759</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>41.82317835817143</v>
+        <v>41.8224142563882</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1.605823490812416</v>
@@ -689,16 +689,16 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.604932363122009</v>
+        <v>1.604913983844917</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5617.479517341883</v>
+        <v>5617.478278198943</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>29.9117081593422</v>
+        <v>29.9104690164022</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1.584987221195</v>
@@ -723,16 +723,16 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.326816070969439</v>
+        <v>2.326835386042989</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1458.579135446002</v>
+        <v>1458.589957983972</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1387.165085961316</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>71.4140494846863</v>
+        <v>71.42487202265602</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2.554936320648244</v>
@@ -757,16 +757,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2.620443567247455</v>
+        <v>2.620452779953789</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1034.418161051912</v>
+        <v>1034.423776740615</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>110.3837290484507</v>
+        <v>110.3893447371538</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>2.856680702081665</v>
@@ -791,16 +791,16 @@
         <v>0</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.322187357746403</v>
+        <v>1.322183096357835</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>23.98885439361007</v>
+        <v>23.98776938670768</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1.232862224129894</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>22.75599216948018</v>
+        <v>22.75490716257779</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1.295265187087496</v>
@@ -825,16 +825,16 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.895858434240606</v>
+        <v>1.895852608677979</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>387.5942855436776</v>
+        <v>387.5927485006827</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>257.0768060680081</v>
+        <v>257.0752690250131</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1.884383945729727</v>
@@ -859,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.344007799348794</v>
+        <v>2.344028697689152</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>213.8174263397567</v>
+        <v>213.829567210624</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>129.2846172515397</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>84.53280908821705</v>
+        <v>84.54494995908439</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2.500505845296554</v>
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1909.201857117318</v>
+        <v>1907.266107766158</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1925.037208036543</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-15.83535091922545</v>
+        <v>-17.7711002703852</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>-0.8225997322605955</v>
+        <v>-0.9231561964722217</v>
       </c>
     </row>
     <row r="21">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1954.42507915745</v>
+        <v>1953.868610209056</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1959.352995174775</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-4.927916017324151</v>
+        <v>-5.484384965718164</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>-0.2515073102937523</v>
+        <v>-0.2799079583528008</v>
       </c>
     </row>
     <row r="22">
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2114.958163480926</v>
+        <v>2114.283881159667</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2120.558269623172</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-5.600106142246204</v>
+        <v>-6.274388463505147</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>-0.2640864069838249</v>
+        <v>-0.295883803495771</v>
       </c>
     </row>
     <row r="23">
@@ -1719,16 +1719,16 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1917.582693290566</v>
+        <v>1917.285510400524</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1920.371028203399</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-2.788334912833534</v>
+        <v>-3.085517802875302</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-0.1451977181431527</v>
+        <v>-0.1606730031624125</v>
       </c>
     </row>
     <row r="24">
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1966.609134609069</v>
+        <v>1966.35911009856</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1969.206216134805</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-2.597081525735575</v>
+        <v>-2.84710603624444</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>-0.1318846906157536</v>
+        <v>-0.1445814060973662</v>
       </c>
     </row>
     <row r="25">
@@ -1787,16 +1787,16 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1952.261629532552</v>
+        <v>1951.40603722992</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1959.488267660658</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-7.226638128105606</v>
+        <v>-8.082230430737582</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-0.3688023167769794</v>
+        <v>-0.4124663854398363</v>
       </c>
     </row>
     <row r="26">
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1942.464721194208</v>
+        <v>1941.512830001077</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1950.482397570457</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-8.017676376249256</v>
+        <v>-8.969567569380388</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>-0.4110612013846505</v>
+        <v>-0.4598640613497965</v>
       </c>
     </row>
     <row r="27">
@@ -1855,16 +1855,16 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2105.157716599519</v>
+        <v>2104.513936999524</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>2110.486101250903</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-5.328384651384113</v>
+        <v>-5.972164251379127</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>-0.2524719138508391</v>
+        <v>-0.2829757678972334</v>
       </c>
     </row>
     <row r="28">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2065.96831397461</v>
+        <v>2065.002739618501</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>2073.929471749065</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-7.961157774454932</v>
+        <v>-8.926732130564233</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>-0.383868298459582</v>
+        <v>-0.4304260223003535</v>
       </c>
     </row>
     <row r="29">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>382420.1666023619</v>
+        <v>383167.5996365632</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>428113.5341067808</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-45693.36750441889</v>
+        <v>-44945.93447021762</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>-10.67318920429691</v>
+        <v>-10.49860163005431</v>
       </c>
     </row>
     <row r="48">
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>202149.1515720201</v>
+        <v>202360.3016291293</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>216406.9710876753</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-14257.81951565517</v>
+        <v>-14046.66945854592</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>-6.58842894200425</v>
+        <v>-6.490858121596759</v>
       </c>
     </row>
     <row r="49">
@@ -2603,16 +2603,16 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>339952.7654894254</v>
+        <v>340218.1474261827</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>356045.7240370425</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-16092.95854761713</v>
+        <v>-15827.57661085983</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>-4.519913444022388</v>
+        <v>-4.445377529435841</v>
       </c>
     </row>
     <row r="50">
@@ -2637,16 +2637,16 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>208859.630790865</v>
+        <v>208975.7151938569</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>216987.1565901284</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-8127.525799263443</v>
+        <v>-8011.441396271577</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>-3.745625283534959</v>
+        <v>-3.692127000587669</v>
       </c>
     </row>
     <row r="51">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>161531.3544111279</v>
+        <v>161630.1940950605</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>169090.0151412379</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-7558.660730110016</v>
+        <v>-7459.821046177443</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>-4.470199333648647</v>
+        <v>-4.411745448095433</v>
       </c>
     </row>
     <row r="52">
@@ -2705,16 +2705,16 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>288882.375197493</v>
+        <v>289210.4983443036</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>309794.8842831829</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-20912.5090856899</v>
+        <v>-20584.38593887934</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-6.75043719139462</v>
+        <v>-6.644520934071716</v>
       </c>
     </row>
     <row r="53">
@@ -2739,16 +2739,16 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>281148.8412345927</v>
+        <v>281514.3472652387</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>304336.5491684119</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-23187.70793381921</v>
+        <v>-22822.20190317318</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-7.619100629608487</v>
+        <v>-7.499001340960849</v>
       </c>
     </row>
     <row r="54">
@@ -2773,16 +2773,16 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>366364.5005821656</v>
+        <v>366616.7671589082</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>381702.8635022599</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-15338.3629200944</v>
+        <v>-15086.09634335176</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>-4.018403943674786</v>
+        <v>-3.952314165246612</v>
       </c>
     </row>
     <row r="55">
@@ -2807,16 +2807,16 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>352502.9992583847</v>
+        <v>352879.548248544</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>375427.2603331699</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-22924.2610747852</v>
+        <v>-22547.71208462591</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-6.106179144913784</v>
+        <v>-6.005880357386973</v>
       </c>
     </row>
     <row r="56">
@@ -3453,16 +3453,16 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>282974.4314910981</v>
+        <v>283630.2800182434</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>339326.4139217038</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-56351.98243060568</v>
+        <v>-55696.1339034604</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>-16.60701322344106</v>
+        <v>-16.41373368485005</v>
       </c>
     </row>
     <row r="75">
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>125166.0302746638</v>
+        <v>125353.1212499976</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>142390.025306692</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-17223.99503202821</v>
+        <v>-17036.90405669439</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>-12.09634944226583</v>
+        <v>-11.96495612666605</v>
       </c>
     </row>
     <row r="76">
@@ -3521,16 +3521,16 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>257341.4658703297</v>
+        <v>257571.8751482602</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>277141.446043731</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>-19799.98017340127</v>
+        <v>-19569.57089547085</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>-7.144359119161475</v>
+        <v>-7.061221327532119</v>
       </c>
     </row>
     <row r="77">
@@ -3555,16 +3555,16 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>144213.466990081</v>
+        <v>144314.675025019</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>153932.2324693588</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-9718.765479277819</v>
+        <v>-9617.55744433988</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>-6.313664996193959</v>
+        <v>-6.247916560460665</v>
       </c>
     </row>
     <row r="78">
@@ -3589,16 +3589,16 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>86738.10448239291</v>
+        <v>86823.71006856073</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>95597.21893998417</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>-8859.114457591262</v>
+        <v>-8773.508871423444</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>-9.267125713304489</v>
+        <v>-9.17757751606921</v>
       </c>
     </row>
     <row r="79">
@@ -3623,16 +3623,16 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>210554.046905864</v>
+        <v>210843.0576271448</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>236133.8367712313</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>-25579.78986536732</v>
+        <v>-25290.77914408653</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>-10.83275070406333</v>
+        <v>-10.71035794357099</v>
       </c>
     </row>
     <row r="80">
@@ -3657,16 +3657,16 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>200128.0099419135</v>
+        <v>200449.7253461142</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>228514.5085635225</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>-28386.498621609</v>
+        <v>-28064.78321740835</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>-12.42218658239729</v>
+        <v>-12.28140103393343</v>
       </c>
     </row>
     <row r="81">
@@ -3691,16 +3691,16 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>287678.7192170005</v>
+        <v>287898.2733291671</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>306553.9278759986</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>-18875.20865899813</v>
+        <v>-18655.6545468315</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>-6.157222903577727</v>
+        <v>-6.085602841917503</v>
       </c>
     </row>
     <row r="82">
@@ -3725,16 +3725,16 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>266356.2165165095</v>
+        <v>266684.8094360135</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>294592.5200651514</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>-28236.30354864197</v>
+        <v>-27907.71062913793</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>-9.584867783607434</v>
+        <v>-9.473326282339389</v>
       </c>
     </row>
     <row r="83">
@@ -4371,16 +4371,16 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>99445.73511126393</v>
+        <v>99537.3196183199</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>88787.12018507704</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>10658.61492618688</v>
+        <v>10750.19943324286</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>12.00468593188851</v>
+        <v>12.10783659931084</v>
       </c>
     </row>
     <row r="102">
@@ -4405,16 +4405,16 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>76983.12129735632</v>
+        <v>77007.18037913172</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>74016.94578098327</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>2966.175516373056</v>
+        <v>2990.234598148454</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>4.007427603335583</v>
+        <v>4.039932432495367</v>
       </c>
     </row>
     <row r="103">
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>82611.29961909569</v>
+        <v>82646.27227792254</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>78904.27799331152</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>3707.021625784168</v>
+        <v>3741.994284611021</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>4.698125019404398</v>
+        <v>4.742447912555791</v>
       </c>
     </row>
     <row r="104">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>64646.16380078402</v>
+        <v>64661.04016883792</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>63054.9241207696</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1591.239680014427</v>
+        <v>1606.116048068325</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>2.523577186401356</v>
+        <v>2.547169900628408</v>
       </c>
     </row>
     <row r="105">
@@ -4507,16 +4507,16 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>74793.24992873499</v>
+        <v>74806.48402649975</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>73492.79620125376</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1300.453727481232</v>
+        <v>1313.687825245986</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1.76949822935033</v>
+        <v>1.787505569455494</v>
       </c>
     </row>
     <row r="106">
@@ -4541,16 +4541,16 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>78328.32829162902</v>
+        <v>78367.44071715878</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>73661.0475119516</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>4667.280779677414</v>
+        <v>4706.393205207176</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>6.336158576783939</v>
+        <v>6.389256417299194</v>
       </c>
     </row>
     <row r="107">
@@ -4575,16 +4575,16 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>81020.83129267913</v>
+        <v>81064.62191912455</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>75822.04060488936</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>5198.790687789762</v>
+        <v>5242.581314235184</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>6.856569206414262</v>
+        <v>6.914323687955607</v>
       </c>
     </row>
     <row r="108">
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>78685.78136516514</v>
+        <v>78718.49382974103</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>75148.93562626136</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>3536.845738903779</v>
+        <v>3569.558203479668</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>4.706448214374712</v>
+        <v>4.749978391220566</v>
       </c>
     </row>
     <row r="109">
@@ -4643,16 +4643,16 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>86146.78274187521</v>
+        <v>86194.73881253046</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>80834.74026801846</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>5312.042473856753</v>
+        <v>5359.998544511996</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>6.571484557560229</v>
+        <v>6.630810622685494</v>
       </c>
     </row>
     <row r="110">
@@ -5289,16 +5289,16 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>200.3036845877438</v>
+        <v>200.8988667477238</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>222.3923425061683</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>-22.08865791842447</v>
+        <v>-21.49347575844448</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>-9.932292483412203</v>
+        <v>-9.664665391007485</v>
       </c>
     </row>
     <row r="129">
@@ -5323,16 +5323,16 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>103.4315173949601</v>
+        <v>103.5690427553762</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>110.4481793840174</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>-7.016661989057297</v>
+        <v>-6.879136628641135</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>-6.352899638717501</v>
+        <v>-6.228383905472138</v>
       </c>
     </row>
     <row r="130">
@@ -5357,16 +5357,16 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>160.7373476030895</v>
+        <v>160.9141281631377</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>167.9018818475159</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>-7.164534244426335</v>
+        <v>-6.98775368437822</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>-4.267095857170307</v>
+        <v>-4.16180784127501</v>
       </c>
     </row>
     <row r="131">
@@ -5391,16 +5391,16 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>108.9181872164598</v>
+        <v>108.9956159686418</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>112.9923089878785</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>-4.074121771418731</v>
+        <v>-3.996693019236716</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>-3.605662905654748</v>
+        <v>-3.537137222025855</v>
       </c>
     </row>
     <row r="132">
@@ -5425,16 +5425,16 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>82.13698979041801</v>
+        <v>82.19769891724359</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>85.86709393652586</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>-3.730104146107848</v>
+        <v>-3.669395019282277</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>-4.344043771721438</v>
+        <v>-4.273342500672894</v>
       </c>
     </row>
     <row r="133">
@@ -5459,16 +5459,16 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>147.9731870090909</v>
+        <v>148.2062127648465</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>158.0998924035573</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>-10.12670539446637</v>
+        <v>-9.893679638710807</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>-6.405257613090264</v>
+        <v>-6.257866142917246</v>
       </c>
     </row>
     <row r="134">
@@ -5493,16 +5493,16 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>144.7381968727572</v>
+        <v>144.9974179491168</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>156.0314256347542</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>-11.29322876199703</v>
+        <v>-11.03400768563739</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>-7.23779117960042</v>
+        <v>-7.071657290029716</v>
       </c>
     </row>
     <row r="135">
@@ -5527,16 +5527,16 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>174.0318540949785</v>
+        <v>174.2049604487799</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>180.8601645260878</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-6.828310431109315</v>
+        <v>-6.6552040773079</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>-3.775464016082093</v>
+        <v>-3.679751201568731</v>
       </c>
     </row>
     <row r="136">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>170.6236232540384</v>
+        <v>170.8857530686554</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>181.0221926286386</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>-10.39856937460024</v>
+        <v>-10.13643955998322</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>-5.744361629699505</v>
+        <v>-5.599556282459691</v>
       </c>
     </row>
     <row r="137">
@@ -6207,16 +6207,16 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>65.88025867471156</v>
+        <v>65.9454288799174</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>34.88609571089764</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>30.99416296381391</v>
+        <v>31.05933316901976</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>88.84388560033683</v>
+        <v>89.0306941378869</v>
       </c>
     </row>
     <row r="156">
@@ -6241,16 +6241,16 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>70.13487334504799</v>
+        <v>70.16524832444252</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>51.54670887456342</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>18.58816447048457</v>
+        <v>18.61853944987909</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>36.0608172205873</v>
+        <v>36.11974431808336</v>
       </c>
     </row>
     <row r="157">
@@ -6275,16 +6275,16 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>47.54234951711562</v>
+        <v>47.58272192007493</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>35.33710677770379</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>12.20524273941184</v>
+        <v>12.24561514237114</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>34.53945116727221</v>
+        <v>34.65370048375779</v>
       </c>
     </row>
     <row r="158">
@@ -6309,16 +6309,16 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>55.8418724933398</v>
+        <v>55.86597841117869</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>46.10651242373578</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>9.73536006960402</v>
+        <v>9.759465987442908</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>21.11493487109258</v>
+        <v>21.16721797942519</v>
       </c>
     </row>
     <row r="159">
@@ -6343,16 +6343,16 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>74.72536134271866</v>
+        <v>74.7403243309566</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>62.70118854923339</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>12.02417279348527</v>
+        <v>12.03913578172321</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>19.17694555988171</v>
+        <v>19.20080952256591</v>
       </c>
     </row>
     <row r="160">
@@ -6377,16 +6377,16 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>57.7276005372099</v>
+        <v>57.7747342097537</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>39.04230813560093</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>18.68529240160896</v>
+        <v>18.73242607415276</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>47.85908747175396</v>
+        <v>47.97981207743069</v>
       </c>
     </row>
     <row r="161">
@@ -6411,16 +6411,16 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>61.75253871025515</v>
+        <v>61.80125424659402</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>40.30535362004972</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>21.44718509020543</v>
+        <v>21.4959006265443</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>53.21175269266617</v>
+        <v>53.33261886046636</v>
       </c>
     </row>
     <row r="162">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>43.54824233174803</v>
+        <v>43.58660351983809</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>32.86765362228716</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>10.68058870946087</v>
+        <v>10.71894989755093</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>32.49574439417389</v>
+        <v>32.61245850017885</v>
       </c>
     </row>
     <row r="163">
@@ -6479,16 +6479,16 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>51.76922671320879</v>
+        <v>51.81994003371823</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>34.96602915887432</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>16.80319755433447</v>
+        <v>16.85391087484391</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>48.05577859008861</v>
+        <v>48.20081456280093</v>
       </c>
     </row>
   </sheetData>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F20" t="n">
-        <v>970.2255008807361</v>
+        <v>974.5334493114932</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F21" t="n">
-        <v>29.77449911926391</v>
+        <v>25.46655068850678</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F22" t="n">
-        <v>291.0676502642208</v>
+        <v>292.3600347934479</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F23" t="n">
-        <v>8.932349735779173</v>
+        <v>7.639965206552033</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F24" t="n">
-        <v>339.5789253082576</v>
+        <v>341.0867072590226</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F25" t="n">
-        <v>10.42107469174237</v>
+        <v>8.913292740977372</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F26" t="n">
-        <v>161.7042501467893</v>
+        <v>162.4222415519155</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F27" t="n">
-        <v>4.962416519877318</v>
+        <v>4.244425114751129</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F28" t="n">
-        <v>145.5338251321104</v>
+        <v>146.180017396724</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F29" t="n">
-        <v>4.466174867889587</v>
+        <v>3.819982603276017</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -7643,10 +7643,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F30" t="n">
-        <v>436.6014753963312</v>
+        <v>438.5400521901719</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F31" t="n">
-        <v>13.39852460366876</v>
+        <v>11.45994780982805</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F32" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F33" t="n">
-        <v>14.88724955963196</v>
+        <v>12.73327534425339</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F34" t="n">
-        <v>323.4085002935787</v>
+        <v>324.8444831038311</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F35" t="n">
-        <v>9.924833039754636</v>
+        <v>8.488850229502258</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F36" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.02977449911926391</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F37" t="n">
-        <v>14.88724955963196</v>
+        <v>12.73327534425339</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -18326,28 +18326,28 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>24.5854853165744</v>
+        <v>24.69463727684086</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>137373.0663280211</v>
+        <v>137982.9603075152</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>35.92202460150611</v>
+        <v>36.01112422824708</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>15.75980730763606</v>
+        <v>15.82977598382447</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.2267656271348852</v>
+        <v>0.227772396470699</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>17.02444631024793</v>
+        <v>17.10002959295669</v>
       </c>
     </row>
     <row r="183">
@@ -18380,25 +18380,25 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>970.2255008807361</v>
+        <v>974.5334493114932</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>971.1163916193452</v>
+        <v>975.429825520984</v>
       </c>
       <c r="I183" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>126747.6637116642</v>
+        <v>127310.642232391</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>126631.3868979727</v>
+        <v>127193.6494688663</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>33.14356165830961</v>
+        <v>33.22583703662467</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>747.4002125697966</v>
+        <v>750.719960277499</v>
       </c>
       <c r="N183" s="2" t="n">
         <v>0</v>
@@ -18440,28 +18440,28 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>28.41344360645446</v>
+        <v>28.53769053024471</v>
       </c>
       <c r="I184" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46469.9906252039</v>
+        <v>46673.1956102706</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>12.15155336552193</v>
+        <v>12.18088263583362</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>17.51112265616906</v>
+        <v>17.58769567393761</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.08890282259869514</v>
+        <v>0.0892915787937256</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>9.221917979931277</v>
+        <v>9.24703824892501</v>
       </c>
     </row>
     <row r="185">
@@ -18497,28 +18497,28 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>4.582912280468757</v>
+        <v>4.602952538901897</v>
       </c>
       <c r="I185" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>21992.93375711776</v>
+        <v>22089.10493588413</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L185" s="2" t="n">
-        <v>5.750986919051754</v>
+        <v>5.764867634120363</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2.824435509377034</v>
+        <v>2.836786262363705</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.02099246635079879</v>
+        <v>0.02108426266394488</v>
       </c>
       <c r="O185" s="2" t="n">
-        <v>2.666565316804391</v>
+        <v>2.673828972607149</v>
       </c>
     </row>
     <row r="186">
@@ -18554,28 +18554,28 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>10.52146317696673</v>
+        <v>10.56747165983902</v>
       </c>
       <c r="I186" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>9722.194250573779</v>
+        <v>9764.707672912014</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>2.542280742396845</v>
+        <v>2.54841685000869</v>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6.484347155033949</v>
+        <v>6.512702049215725</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.009699695467756425</v>
+        <v>0.009742110506928128</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>1.354469464465739</v>
+        <v>1.387316273853757</v>
       </c>
     </row>
     <row r="187">
@@ -18611,28 +18611,28 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>22.16098781069713</v>
+        <v>22.21519839783379</v>
       </c>
       <c r="I187" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>9356.039291235316</v>
+        <v>9378.926194453892</v>
       </c>
       <c r="K187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L187" s="2" t="n">
-        <v>2.446533971876977</v>
+        <v>2.447734673638862</v>
       </c>
       <c r="M187" s="2" t="n">
-        <v>166.1677295349941</v>
+        <v>166.5742118749604</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.00100448853042484</v>
+        <v>0.00100694572743571</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>4.151332359967859</v>
+        <v>4.161487420137362</v>
       </c>
     </row>
     <row r="188">
@@ -18668,28 +18668,28 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>11.70508039237595</v>
+        <v>11.60487581551754</v>
       </c>
       <c r="I188" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>5219.861238373764</v>
+        <v>5175.175173082701</v>
       </c>
       <c r="K188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
-        <v>1.364954490959506</v>
+        <v>1.350629640395322</v>
       </c>
       <c r="M188" s="2" t="n">
-        <v>121.8250947672359</v>
+        <v>120.7821773619153</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.0004672034615092486</v>
+        <v>0.0004632038371070266</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>2.192667557239483</v>
+        <v>2.173896620398463</v>
       </c>
     </row>
     <row r="189">
@@ -18722,25 +18722,25 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>29.77449911926391</v>
+        <v>25.46655068850678</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>29.91380397165307</v>
+        <v>25.60212928579547</v>
       </c>
       <c r="I189" s="2" t="n">
         <v>129.2846172515397</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>3867.394697012754</v>
+        <v>3309.961485538501</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>3849.384722490339</v>
+        <v>3292.433258480532</v>
       </c>
       <c r="L189" s="2" t="n">
-        <v>1.011294653044291</v>
+        <v>0.8638416945164518</v>
       </c>
       <c r="M189" s="2" t="n">
-        <v>14.50021674107932</v>
+        <v>12.41020446710688</v>
       </c>
       <c r="N189" s="2" t="n">
         <v>0</v>
@@ -18782,28 +18782,28 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>2.003193852010857</v>
+        <v>2.012087413920466</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>1387.165085961316</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>2778.76057192182</v>
+        <v>2791.097410492664</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>0.7266250095045741</v>
+        <v>0.7284273026059711</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1.28408891266626</v>
+        <v>1.289789870779114</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.01507861159528108</v>
+        <v>0.01514555597293028</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>0.924430084201161</v>
+        <v>0.9285342682154513</v>
       </c>
     </row>
     <row r="191">
@@ -18839,28 +18839,28 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>5.586348987904699</v>
+        <v>5.596911769819069</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>2536.664767213387</v>
+        <v>2541.461144379217</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>0.6633187757200564</v>
+        <v>0.6632766305892795</v>
       </c>
       <c r="M191" s="2" t="n">
-        <v>35.92837732376665</v>
+        <v>35.99631142796061</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.004808341582610705</v>
+        <v>0.00481743329235116</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>0.4982189124281324</v>
+        <v>0.4991609548477856</v>
       </c>
     </row>
     <row r="192">
@@ -18896,28 +18896,28 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>7.463299186008485</v>
+        <v>7.494435935155343</v>
       </c>
       <c r="I192" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>41701.69028203927</v>
+        <v>41875.66897925485</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>20.62916908517527</v>
+        <v>20.69361858137641</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4.784129966775018</v>
+        <v>4.804089270421949</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.06883816604057605</v>
+        <v>0.06912535762358982</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>5.168030431510806</v>
+        <v>5.189591360949485</v>
       </c>
     </row>
     <row r="193">
@@ -18950,25 +18950,25 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>291.0676502642208</v>
+        <v>292.3600347934479</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>294.3841229998835</v>
+        <v>295.6153781720723</v>
       </c>
       <c r="I193" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>38422.27373160027</v>
+        <v>38582.97405326573</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>37989.41606939181</v>
+        <v>38158.09484065988</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>19.00689339173976</v>
+        <v>19.06647387983128</v>
       </c>
       <c r="M193" s="2" t="n">
-        <v>226.5668235095858</v>
+        <v>227.5144343061528</v>
       </c>
       <c r="N193" s="2" t="n">
         <v>0</v>
@@ -19010,28 +19010,28 @@
         <v>50</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>84.18637844935719</v>
+        <v>84.20184907719651</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>35542.23626163415</v>
+        <v>35548.76773050012</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>21109.25598433646</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>17.58218423636146</v>
+        <v>17.56706599284044</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>631.247103432407</v>
+        <v>631.3631054411848</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.003815906235441589</v>
+        <v>0.003816607470799679</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>15.77030952368559</v>
+        <v>15.77320757672036</v>
       </c>
     </row>
     <row r="195">
@@ -19067,28 +19067,28 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>9.022297412332211</v>
+        <v>9.056968855859356</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>14755.90505593056</v>
+        <v>14812.60996217088</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L195" s="2" t="n">
-        <v>7.299513721022689</v>
+        <v>7.319918898578396</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5.56041565450717</v>
+        <v>5.581783564313511</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.02822986602366733</v>
+        <v>0.02833834950197527</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>2.928292954542591</v>
+        <v>2.934720219938411</v>
       </c>
     </row>
     <row r="196">
@@ -19124,28 +19124,28 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46.68810873985096</v>
+        <v>46.64858986891273</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>11353.15656011375</v>
+        <v>11343.54674851609</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>5.616227657561518</v>
+        <v>5.605618620447448</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>38.43454111404539</v>
+        <v>38.40200842615435</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.04412822903130228</v>
+        <v>0.04409087695526215</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>5.562958261863566</v>
+        <v>5.558249529050885</v>
       </c>
     </row>
     <row r="197">
@@ -19181,28 +19181,28 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>16.10489915891709</v>
+        <v>16.07628770675517</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>7181.95313910916</v>
+        <v>7169.19390934677</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>3.552799051224527</v>
+        <v>3.542786728241751</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>167.6178890261856</v>
+        <v>167.3201044100864</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.0006428204149032881</v>
+        <v>0.0006416784005778196</v>
       </c>
       <c r="O197" s="2" t="n">
-        <v>3.016868634355701</v>
+        <v>3.011508961391661</v>
       </c>
     </row>
     <row r="198">
@@ -19238,28 +19238,28 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1.455240631220989</v>
+        <v>1.460832920086885</v>
       </c>
       <c r="I198" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>6983.552999586511</v>
+        <v>7010.389829761611</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>3.454653628411825</v>
+        <v>3.464310822490136</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>0.8968605685571622</v>
+        <v>0.9003070799204379</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.006665868363532616</v>
+        <v>0.006691484375504215</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>0.8467310647328181</v>
+        <v>0.8485895417897262</v>
       </c>
     </row>
     <row r="199">
@@ -19295,28 +19295,28 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>15.26095628712189</v>
+        <v>15.26394408666446</v>
       </c>
       <c r="I199" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>6929.737152358899</v>
+        <v>6931.093860621762</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L199" s="2" t="n">
-        <v>3.428031776769554</v>
+        <v>3.425125286344229</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>98.15022244266886</v>
+        <v>98.16943835445051</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.01313557224309673</v>
+        <v>0.01313814393362522</v>
       </c>
       <c r="O199" s="2" t="n">
-        <v>1.361049418939891</v>
+        <v>1.361315886044233</v>
       </c>
     </row>
     <row r="200">
@@ -19352,28 +19352,28 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>34.07776180508898</v>
+        <v>34.07759460036603</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>5078.752414557148</v>
+        <v>5078.727495332839</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>2.51237879311491</v>
+        <v>2.509744971936614</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>43.39356417876146</v>
+        <v>43.39335126545696</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.02062098937908996</v>
+        <v>0.02062088820088361</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>0.8297714904854758</v>
+        <v>0.8297674191584631</v>
       </c>
     </row>
     <row r="201">
@@ -19409,28 +19409,28 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>4.6943417576596</v>
+        <v>4.692401962210954</v>
       </c>
       <c r="I201" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>4630.331754185957</v>
+        <v>4628.418408944776</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L201" s="2" t="n">
-        <v>2.290552158234658</v>
+        <v>2.2872165991467</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>30.41707828627485</v>
+        <v>30.40450934411707</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.140409515392764</v>
+        <v>0.1403514953863464</v>
       </c>
       <c r="O201" s="2" t="n">
-        <v>0.01265449918109207</v>
+        <v>0.01264927009016013</v>
       </c>
     </row>
     <row r="202">
@@ -19466,28 +19466,28 @@
         <v>250</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>297.9506855347852</v>
+        <v>297.9697221007649</v>
       </c>
       <c r="I202" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>125790.3458332463</v>
+        <v>125798.3827881329</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>105546.2799216823</v>
       </c>
       <c r="L202" s="2" t="n">
-        <v>37.00230108501917</v>
+        <v>36.97580030337077</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2234.096663543664</v>
+        <v>2234.239403703715</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.01350517624974476</v>
+        <v>0.01350603911796835</v>
       </c>
       <c r="O202" s="2" t="n">
-        <v>55.81395256840095</v>
+        <v>55.81751861487185</v>
       </c>
     </row>
     <row r="203">
@@ -19523,28 +19523,28 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>8.644778092045117</v>
+        <v>8.683125522440156</v>
       </c>
       <c r="I203" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>48303.28378463776</v>
+        <v>48517.55265227795</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>14.20882213300903</v>
+        <v>14.26071860637735</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5.541482512694513</v>
+        <v>5.566064012957246</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.07973560416816169</v>
+        <v>0.08008930388124728</v>
       </c>
       <c r="O203" s="2" t="n">
-        <v>5.986156408830894</v>
+        <v>6.012710441077562</v>
       </c>
     </row>
     <row r="204">
@@ -19577,25 +19577,25 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>339.5789253082576</v>
+        <v>341.0867072590226</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>341.2444229520478</v>
+        <v>342.758738601685</v>
       </c>
       <c r="I204" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>44538.3619688306</v>
+        <v>44736.0066305518</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>44320.98541429044</v>
+        <v>44517.77731410319</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>13.10133832996161</v>
+        <v>13.14921234184258</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>262.6319115336179</v>
+        <v>263.797374137487</v>
       </c>
       <c r="N204" s="2" t="n">
         <v>0</v>
@@ -19637,28 +19637,28 @@
         <v>400</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>500.7261407768431</v>
+        <v>500.729684241985</v>
       </c>
       <c r="I205" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>33945.08074724757</v>
+        <v>33945.32096480479</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>27116.68353849796</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>9.985234477612588</v>
+        <v>9.977516255851672</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>11.31533655912466</v>
+        <v>11.31541663383497</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.04063158099479209</v>
+        <v>0.04063186853039127</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>12.04925904132412</v>
+        <v>12.04934430974916</v>
       </c>
     </row>
     <row r="206">
@@ -19694,28 +19694,28 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>10.2028588926216</v>
+        <v>10.24755355177304</v>
       </c>
       <c r="I206" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>16686.70519692657</v>
+        <v>16759.80300304017</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>4.908536388254688</v>
+        <v>4.926193129270552</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>6.287992261230046</v>
+        <v>6.315537449673829</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>0.03192372479357646</v>
+        <v>0.03206356991086268</v>
       </c>
       <c r="O206" s="2" t="n">
-        <v>3.311458096096283</v>
+        <v>3.320504143484384</v>
       </c>
     </row>
     <row r="207">
@@ -19751,28 +19751,28 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>19.61944880384151</v>
+        <v>19.61600877114444</v>
       </c>
       <c r="I207" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>14744.9615254025</v>
+        <v>14742.37617500497</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L207" s="2" t="n">
-        <v>4.33735595713551</v>
+        <v>4.333212759676092</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>315.5231378234415</v>
+        <v>315.4678146631608</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>9.646022077287881</v>
+        <v>9.644330764159044</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>0.4019733181555624</v>
+        <v>0.4019028370033328</v>
       </c>
     </row>
     <row r="208">
@@ -19808,28 +19808,28 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>19.31093156719468</v>
+        <v>19.27576414466843</v>
       </c>
       <c r="I208" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>8611.677988144676</v>
+        <v>8595.995134243232</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L208" s="2" t="n">
-        <v>2.533198391766739</v>
+        <v>2.526612762803404</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>200.9858958123369</v>
+        <v>200.6198774307143</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0007707878776328696</v>
+        <v>0.0007693841844512897</v>
       </c>
       <c r="O208" s="2" t="n">
-        <v>3.617442318041586</v>
+        <v>3.610854540439028</v>
       </c>
     </row>
     <row r="209">
@@ -19865,28 +19865,28 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>147.5415534551076</v>
+        <v>147.5202622533353</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>8491.744468272489</v>
+        <v>8490.519054545719</v>
       </c>
       <c r="K209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>2.497918925897555</v>
+        <v>2.495610277928491</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7.483459703414258</v>
+        <v>7.482379791709596</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.05006147951831471</v>
+        <v>0.05005425532257809</v>
       </c>
       <c r="O209" s="2" t="n">
-        <v>3.550376647366433</v>
+        <v>3.54986430502086</v>
       </c>
     </row>
     <row r="210">
@@ -19922,28 +19922,28 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>1.645657878099068</v>
+        <v>1.652866849497733</v>
       </c>
       <c r="I210" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>7897.346160029453</v>
+        <v>7931.941286605078</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L210" s="2" t="n">
-        <v>2.323071603391651</v>
+        <v>2.331428040100676</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1.014214163993042</v>
+        <v>1.018657032099257</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.007538092705406982</v>
+        <v>0.007571114085753994</v>
       </c>
       <c r="O210" s="2" t="n">
-        <v>0.9575252486866352</v>
+        <v>0.9601409601115011</v>
       </c>
     </row>
     <row r="211">
@@ -19979,28 +19979,28 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>170.9598218990977</v>
+        <v>169.875157250595</v>
       </c>
       <c r="I211" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>7500.727034585827</v>
+        <v>7453.138230607744</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L211" s="2" t="n">
-        <v>2.206402711208168</v>
+        <v>2.190693908303305</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>35.36347300341912</v>
+        <v>35.13910736833014</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.00214327848998465</v>
+        <v>0.002129680333504616</v>
       </c>
       <c r="O211" s="2" t="n">
-        <v>4.113903812821031</v>
+        <v>4.087802908038028</v>
       </c>
     </row>
     <row r="212">
@@ -20036,28 +20036,28 @@
         <v>166.6666666666667</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>212.7879955540517</v>
+        <v>212.7963588885684</v>
       </c>
       <c r="I212" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>89835.92537088651</v>
+        <v>89839.45624627045</v>
       </c>
       <c r="K212" s="2" t="n">
         <v>70364.18661445485</v>
       </c>
       <c r="L212" s="2" t="n">
-        <v>43.01258459124678</v>
+        <v>42.99038104161081</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1595.528971702769</v>
+        <v>1595.591681737171</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.009645016854481674</v>
+        <v>0.009645395938377661</v>
       </c>
       <c r="O212" s="2" t="n">
-        <v>39.86075437169077</v>
+        <v>39.86232104288401</v>
       </c>
     </row>
     <row r="213">
@@ -20093,28 +20093,28 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>4.198820973461658</v>
+        <v>4.215665081311766</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>23461.19690783486</v>
+        <v>23555.31450263252</v>
       </c>
       <c r="K213" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L213" s="2" t="n">
-        <v>11.2329974054809</v>
+        <v>11.27179513695233</v>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2.69153155241585</v>
+        <v>2.702328975796701</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.03872806491366057</v>
+        <v>0.03888342750386262</v>
       </c>
       <c r="O213" s="2" t="n">
-        <v>2.907512351641507</v>
+        <v>2.919176209647387</v>
       </c>
     </row>
     <row r="214">
@@ -20147,25 +20147,25 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>161.7042501467893</v>
+        <v>162.4222415519155</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>165.4153928865426</v>
+        <v>166.080744523857</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>21589.60014602913</v>
+        <v>21676.44016469642</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>21105.23114966211</v>
+        <v>21198.94157814438</v>
       </c>
       <c r="L214" s="2" t="n">
-        <v>10.33689471932812</v>
+        <v>10.3727077304596</v>
       </c>
       <c r="M214" s="2" t="n">
-        <v>127.3086324900373</v>
+        <v>127.8207070049502</v>
       </c>
       <c r="N214" s="2" t="n">
         <v>0</v>
@@ -20207,28 +20207,28 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>44.6893252515405</v>
+        <v>44.66787513035706</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>10867.11198720112</v>
+        <v>10861.89595702552</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L215" s="2" t="n">
-        <v>5.203069614770393</v>
+        <v>5.197683351364273</v>
       </c>
       <c r="M215" s="2" t="n">
-        <v>36.78910444434428</v>
+        <v>36.77144629568977</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.04223903758755328</v>
+        <v>0.04221876356305581</v>
       </c>
       <c r="O215" s="2" t="n">
-        <v>5.324800207916045</v>
+        <v>5.322244393768158</v>
       </c>
     </row>
     <row r="216">
@@ -20264,28 +20264,28 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>5.271840557536063</v>
+        <v>5.291291512975024</v>
       </c>
       <c r="I216" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>8622.058792994023</v>
+        <v>8653.87069616983</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L216" s="2" t="n">
-        <v>4.128159549236899</v>
+        <v>4.141089163466694</v>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3.249020002834503</v>
+        <v>3.261007570099808</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.01649506171609441</v>
+        <v>0.0165559218098133</v>
       </c>
       <c r="O216" s="2" t="n">
-        <v>1.711037982521376</v>
+        <v>1.714531698170769</v>
       </c>
     </row>
     <row r="217">
@@ -20321,28 +20321,28 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>15.48998232275669</v>
+        <v>15.47452868215006</v>
       </c>
       <c r="I217" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>6907.731993222132</v>
+        <v>6900.840467757102</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L217" s="2" t="n">
-        <v>3.307356221528023</v>
+        <v>3.302221246787227</v>
       </c>
       <c r="M217" s="2" t="n">
-        <v>161.2179071953898</v>
+        <v>161.0570675284852</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.0006182762627262914</v>
+        <v>0.0006176594370281922</v>
       </c>
       <c r="O217" s="2" t="n">
-        <v>2.901678635496105</v>
+        <v>2.898783764614103</v>
       </c>
     </row>
     <row r="218">
@@ -20378,28 +20378,28 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>12.48576788217993</v>
+        <v>12.48740702545687</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>5669.571941693137</v>
+        <v>5670.316248396503</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
-        <v>2.714536993206784</v>
+        <v>2.713385257773335</v>
       </c>
       <c r="M218" s="2" t="n">
-        <v>80.30171058399692</v>
+        <v>80.31225266761351</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.01074688262919086</v>
+        <v>0.01074829348998661</v>
       </c>
       <c r="O218" s="2" t="n">
-        <v>1.113544053291057</v>
+        <v>1.113690240395107</v>
       </c>
     </row>
     <row r="219">
@@ -20435,28 +20435,28 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>4.345122759859251</v>
+        <v>4.344073425133409</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>4285.87455482642</v>
+        <v>4284.83952837273</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L219" s="2" t="n">
-        <v>2.052035876247404</v>
+        <v>2.050400700578002</v>
       </c>
       <c r="M219" s="2" t="n">
-        <v>28.15430703025887</v>
+        <v>28.14750784559099</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.1299642447289724</v>
+        <v>0.129932858735377</v>
       </c>
       <c r="O219" s="2" t="n">
-        <v>0.01171311234778883</v>
+        <v>0.01171028366463912</v>
       </c>
     </row>
     <row r="220">
@@ -20492,28 +20492,28 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>0.8503151946818919</v>
+        <v>0.8534525131914938</v>
       </c>
       <c r="I220" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>4080.576848264863</v>
+        <v>4095.632523332159</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L220" s="2" t="n">
-        <v>1.95374129160978</v>
+        <v>1.959860512755195</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>0.5240467814009153</v>
+        <v>0.5259803016737142</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.003894949765459345</v>
+        <v>0.003909320551809596</v>
       </c>
       <c r="O220" s="2" t="n">
-        <v>0.4947554890268565</v>
+        <v>0.495765714990449</v>
       </c>
     </row>
     <row r="221">
@@ -20549,28 +20549,28 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>25.9314350653375</v>
+        <v>25.93135052851895</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>3864.671019308184</v>
+        <v>3864.658420429955</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L221" s="2" t="n">
-        <v>1.850367639104922</v>
+        <v>1.849333745236806</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>33.02028455363723</v>
+        <v>33.02017690707634</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.01569151900659837</v>
+        <v>0.01569146785204053</v>
       </c>
       <c r="O221" s="2" t="n">
-        <v>0.631413695760359</v>
+        <v>0.6314116373434263</v>
       </c>
     </row>
     <row r="222">
@@ -20606,28 +20606,28 @@
         <v>50</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>86.33381820090872</v>
+        <v>86.34089026749916</v>
       </c>
       <c r="I222" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>36448.85337016297</v>
+        <v>36451.83909144289</v>
       </c>
       <c r="K222" s="2" t="n">
         <v>21109.25598433646</v>
       </c>
       <c r="L222" s="2" t="n">
-        <v>22.56456865791748</v>
+        <v>22.55261728511212</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>647.3490565978821</v>
+        <v>647.40208443484</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.00391324298859709</v>
+        <v>0.003913563543341182</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>16.1725811285368</v>
+        <v>16.1739059114905</v>
       </c>
     </row>
     <row r="223">
@@ -20663,28 +20663,28 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>3.797146814802256</v>
+        <v>3.811394369511834</v>
       </c>
       <c r="I223" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>21216.8153091291</v>
+        <v>21296.42448718391</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L223" s="2" t="n">
-        <v>13.13479688601402</v>
+        <v>13.17601863093645</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2.434050064480308</v>
+        <v>2.443183043306501</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.03502320038406469</v>
+        <v>0.03515461351816615</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>2.629369371738606</v>
+        <v>2.639235222547824</v>
       </c>
     </row>
     <row r="224">
@@ -20717,25 +20717,25 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>145.5338251321104</v>
+        <v>146.180017396724</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>149.4752902220741</v>
+        <v>150.037823725102</v>
       </c>
       <c r="I224" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>19509.1381236793</v>
+        <v>19582.55857861513</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>18994.7080346959</v>
+        <v>19079.04742032994</v>
       </c>
       <c r="L224" s="2" t="n">
-        <v>12.07761687803648</v>
+        <v>12.11565616700177</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>115.0406528507048</v>
+        <v>115.4735954550817</v>
       </c>
       <c r="N224" s="2" t="n">
         <v>0</v>
@@ -20777,28 +20777,28 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>63.87149250826143</v>
+        <v>63.85332395062092</v>
       </c>
       <c r="I225" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>15531.64336158841</v>
+        <v>15527.22530986322</v>
       </c>
       <c r="K225" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L225" s="2" t="n">
-        <v>9.615249880253858</v>
+        <v>9.606636555005993</v>
       </c>
       <c r="M225" s="2" t="n">
-        <v>52.58023019315073</v>
+        <v>52.56527349016007</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0603694586491118</v>
+        <v>0.06035228626208717</v>
       </c>
       <c r="O225" s="2" t="n">
-        <v>7.610384239940493</v>
+        <v>7.608219429016247</v>
       </c>
     </row>
     <row r="226">
@@ -20834,28 +20834,28 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>17.67689534863876</v>
+        <v>17.67828979909078</v>
       </c>
       <c r="I226" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>8026.773429604272</v>
+        <v>8027.406625514321</v>
       </c>
       <c r="K226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L226" s="2" t="n">
-        <v>4.969173606490423</v>
+        <v>4.966526626078983</v>
       </c>
       <c r="M226" s="2" t="n">
-        <v>113.6882366951514</v>
+        <v>113.6972050467721</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.01521504494981392</v>
+        <v>0.01521624519600474</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>1.576515107590511</v>
+        <v>1.576639471748414</v>
       </c>
     </row>
     <row r="227">
@@ -20891,28 +20891,28 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>4.878875270163989</v>
+        <v>4.895570799588713</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>7979.366781665182</v>
+        <v>8006.672204640154</v>
       </c>
       <c r="K227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>4.93982534273574</v>
+        <v>4.953698316993385</v>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3.006836639138807</v>
+        <v>3.0171260453655</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>0.01526551264367052</v>
+        <v>0.01531775128504028</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>1.583496467339381</v>
+        <v>1.586306726051985</v>
       </c>
     </row>
     <row r="228">
@@ -20948,28 +20948,28 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>17.4572882599977</v>
+        <v>17.44422534697549</v>
       </c>
       <c r="I228" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>7785.048821606807</v>
+        <v>7779.223437153292</v>
       </c>
       <c r="K228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L228" s="2" t="n">
-        <v>4.819527979560168</v>
+        <v>4.812976610408605</v>
       </c>
       <c r="M228" s="2" t="n">
-        <v>181.6933951208412</v>
+        <v>181.5574378643747</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>0.0006968004687048653</v>
+        <v>0.000696279067913347</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>3.270206467783584</v>
+        <v>3.267759442677673</v>
       </c>
     </row>
     <row r="229">
@@ -21005,28 +21005,28 @@
         <v>0</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>37.42093929824042</v>
+        <v>37.4208698622743</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>5577.00024147577</v>
+        <v>5576.989893141199</v>
       </c>
       <c r="K229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L229" s="2" t="n">
-        <v>3.452580622385699</v>
+        <v>3.45046290661581</v>
       </c>
       <c r="M229" s="2" t="n">
-        <v>47.6506626331674</v>
+        <v>47.6505742155633</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>0.02264399863577165</v>
+        <v>0.02264395661897699</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>0.9111757032185875</v>
+        <v>0.9111740124976584</v>
       </c>
     </row>
     <row r="230">
@@ -21062,28 +21062,28 @@
         <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>5.592060325122636</v>
+        <v>5.591172761517473</v>
       </c>
       <c r="I230" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>5515.809421521109</v>
+        <v>5514.933960347423</v>
       </c>
       <c r="K230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L230" s="2" t="n">
-        <v>3.41469892432297</v>
+        <v>3.412069131776141</v>
       </c>
       <c r="M230" s="2" t="n">
-        <v>36.2338631211266</v>
+        <v>36.22811213556653</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>0.1672606130596312</v>
+        <v>0.1672340657006798</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>0.01507447187657724</v>
+        <v>0.01507207927853165</v>
       </c>
     </row>
     <row r="231">
@@ -21119,28 +21119,28 @@
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>1.289890874962143</v>
+        <v>1.289774238573964</v>
       </c>
       <c r="I231" s="2" t="n">
         <v>2963.345789569951</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>3822.392693323765</v>
+        <v>3822.047059373946</v>
       </c>
       <c r="K231" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>2.366347206867994</v>
+        <v>2.364686301821838</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>29.60384907835741</v>
+        <v>29.60117219607247</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>0.6548135479847663</v>
+        <v>0.6547543374820409</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>0.02642794505855766</v>
+        <v>0.02642555535248372</v>
       </c>
     </row>
     <row r="232">
@@ -21176,28 +21176,28 @@
         <v>150</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>192.6178018542324</v>
+        <v>192.64169441125</v>
       </c>
       <c r="I232" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>81320.3697296238</v>
+        <v>81330.45681166789</v>
       </c>
       <c r="K232" s="2" t="n">
         <v>63327.76795300938</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>28.14999346153587</v>
+        <v>28.12154374660508</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1444.288633500779</v>
+        <v>1444.467784899007</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>0.008730764818381732</v>
+        <v>0.008731847793549253</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>36.08234979297151</v>
+        <v>36.08682549351144</v>
       </c>
     </row>
     <row r="233">
@@ -21233,28 +21233,28 @@
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>11.13130161496497</v>
+        <v>11.17940094139434</v>
       </c>
       <c r="I233" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>62196.90257807991</v>
+        <v>62465.66082607999</v>
       </c>
       <c r="K233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L233" s="2" t="n">
-        <v>21.53018249575084</v>
+        <v>21.59868372126483</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7.135395794556927</v>
+        <v>7.166228462954277</v>
       </c>
       <c r="N233" s="2" t="n">
-        <v>0.1026701958103465</v>
+        <v>0.1031138426931342</v>
       </c>
       <c r="O233" s="2" t="n">
-        <v>7.707972580854131</v>
+        <v>7.741279403551006</v>
       </c>
     </row>
     <row r="234">
@@ -21287,25 +21287,25 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>436.6014753963312</v>
+        <v>438.5400521901719</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>439.3793749823446</v>
+        <v>441.2806333000996</v>
       </c>
       <c r="I234" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>57346.68855629068</v>
+        <v>57594.83599975621</v>
       </c>
       <c r="K234" s="2" t="n">
-        <v>56984.12410408771</v>
+        <v>57237.14226098981</v>
       </c>
       <c r="L234" s="2" t="n">
-        <v>19.85122440131071</v>
+        <v>19.91450390960216</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>338.1595049724078</v>
+        <v>339.6227702237241</v>
       </c>
       <c r="N234" s="2" t="n">
         <v>0</v>
@@ -21347,28 +21347,28 @@
         <v>0</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>13.15503538899192</v>
+        <v>13.20932159635034</v>
       </c>
       <c r="I235" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>21514.9694513555</v>
+        <v>21603.75416826502</v>
       </c>
       <c r="K235" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L235" s="2" t="n">
-        <v>7.447657350728614</v>
+        <v>7.469906622319729</v>
       </c>
       <c r="M235" s="2" t="n">
-        <v>8.107410049746775</v>
+        <v>8.140866481454179</v>
       </c>
       <c r="N235" s="2" t="n">
-        <v>0.04116078971861877</v>
+        <v>0.04133064583071795</v>
       </c>
       <c r="O235" s="2" t="n">
-        <v>4.269621769915235</v>
+        <v>4.280202769539087</v>
       </c>
     </row>
     <row r="236">
@@ -21404,28 +21404,28 @@
         <v>0</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>2.1218256424405</v>
+        <v>2.13058167109401</v>
       </c>
       <c r="I236" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>10182.42723021848</v>
+        <v>10224.44652850895</v>
       </c>
       <c r="K236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L236" s="2" t="n">
-        <v>3.524765823203064</v>
+        <v>3.535295774891545</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1.307674972256441</v>
+        <v>1.31307128724931</v>
       </c>
       <c r="N236" s="2" t="n">
-        <v>0.009719224518222344</v>
+        <v>0.009759332341725487</v>
       </c>
       <c r="O236" s="2" t="n">
-        <v>1.234583234453554</v>
+        <v>1.237642785262343</v>
       </c>
     </row>
     <row r="237">
@@ -21461,28 +21461,28 @@
         <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>32.25272777720835</v>
+        <v>32.19160514001714</v>
       </c>
       <c r="I237" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>7842.902139936728</v>
+        <v>7828.038936261773</v>
       </c>
       <c r="K237" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L237" s="2" t="n">
-        <v>2.714911954934934</v>
+        <v>2.706692523638106</v>
       </c>
       <c r="M237" s="2" t="n">
-        <v>26.5510603288829</v>
+        <v>26.50074300878723</v>
       </c>
       <c r="N237" s="2" t="n">
-        <v>0.03048433094960784</v>
+        <v>0.03042655962826346</v>
       </c>
       <c r="O237" s="2" t="n">
-        <v>3.842960944415211</v>
+        <v>3.835678090413898</v>
       </c>
     </row>
     <row r="238">
@@ -21518,28 +21518,28 @@
         <v>0</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>14.98594333392515</v>
+        <v>14.94177049793229</v>
       </c>
       <c r="I238" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>6682.956639936688</v>
+        <v>6663.257836796609</v>
       </c>
       <c r="K238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="n">
-        <v>2.313383305356693</v>
+        <v>2.303947427546021</v>
       </c>
       <c r="M238" s="2" t="n">
-        <v>155.9719289088349</v>
+        <v>155.5121832470731</v>
       </c>
       <c r="N238" s="2" t="n">
-        <v>0.000598157754145086</v>
+        <v>0.0005963946135951082</v>
       </c>
       <c r="O238" s="2" t="n">
-        <v>2.807258956062331</v>
+        <v>2.798984229093697</v>
       </c>
     </row>
     <row r="239">
@@ -21575,28 +21575,28 @@
         <v>0</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>4.871293404419698</v>
+        <v>4.8913955201523</v>
       </c>
       <c r="I239" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>4501.24283407516</v>
+        <v>4519.817881168203</v>
       </c>
       <c r="K239" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="n">
-        <v>1.558157651880946</v>
+        <v>1.562812521344707</v>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3.00216395733192</v>
+        <v>3.014552832792342</v>
       </c>
       <c r="N239" s="2" t="n">
-        <v>0.004490826205655496</v>
+        <v>0.004509358266984256</v>
       </c>
       <c r="O239" s="2" t="n">
-        <v>0.6271008183713479</v>
+        <v>0.6421510107050548</v>
       </c>
     </row>
     <row r="240">
@@ -21632,28 +21632,28 @@
         <v>0</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>9.690896887692922</v>
+        <v>9.695536246453548</v>
       </c>
       <c r="I240" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>4400.469206441185</v>
+        <v>4402.575859272223</v>
       </c>
       <c r="K240" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="n">
-        <v>1.523273686542083</v>
+        <v>1.522273874730156</v>
       </c>
       <c r="M240" s="2" t="n">
-        <v>62.32661094761647</v>
+        <v>62.35644879563724</v>
       </c>
       <c r="N240" s="2" t="n">
-        <v>0.008341251607942234</v>
+        <v>0.008345244846047062</v>
       </c>
       <c r="O240" s="2" t="n">
-        <v>0.864283294562031</v>
+        <v>0.8646970560869711</v>
       </c>
     </row>
     <row r="241">
@@ -21689,28 +21689,28 @@
         <v>0</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>3.569293241785101</v>
+        <v>3.566296732901693</v>
       </c>
       <c r="I241" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>3520.623910790542</v>
+        <v>3517.66826099962</v>
       </c>
       <c r="K241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L241" s="2" t="n">
-        <v>1.218704986201974</v>
+        <v>1.216300335270628</v>
       </c>
       <c r="M241" s="2" t="n">
-        <v>23.12730465030656</v>
+        <v>23.10788871299365</v>
       </c>
       <c r="N241" s="2" t="n">
-        <v>0.1067588940570812</v>
+        <v>0.1066692673571284</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>0.009621714978793036</v>
+        <v>0.009613637313985325</v>
       </c>
     </row>
     <row r="242">
@@ -21746,28 +21746,28 @@
         <v>0</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>12.35526416708475</v>
+        <v>12.40880651769102</v>
       </c>
       <c r="I242" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>69035.87633394929</v>
+        <v>69335.04784862486</v>
       </c>
       <c r="K242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L242" s="2" t="n">
-        <v>24.55492116944037</v>
+        <v>24.62931233245401</v>
       </c>
       <c r="M242" s="2" t="n">
-        <v>7.919981241001871</v>
+        <v>7.954303001076458</v>
       </c>
       <c r="N242" s="2" t="n">
-        <v>0.1139594842725085</v>
+        <v>0.1144533351994748</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>8.555516751164637</v>
+        <v>8.592592646209363</v>
       </c>
     </row>
     <row r="243">
@@ -21800,25 +21800,25 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>487.7456508761415</v>
+        <v>489.8619617712763</v>
       </c>
       <c r="I243" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>63659.33297757388</v>
+        <v>63935.54854139377</v>
       </c>
       <c r="K243" s="2" t="n">
-        <v>63315.69344898634</v>
+        <v>63596.82473443313</v>
       </c>
       <c r="L243" s="2" t="n">
-        <v>22.64257348457505</v>
+        <v>22.71129310548234</v>
       </c>
       <c r="M243" s="2" t="n">
-        <v>375.383637111661</v>
+        <v>377.0124132568664</v>
       </c>
       <c r="N243" s="2" t="n">
         <v>0</v>
@@ -21860,28 +21860,28 @@
         <v>100</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>137.2011814805265</v>
+        <v>137.2277769797463</v>
       </c>
       <c r="I244" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>57924.29722451672</v>
+        <v>57935.52544853797</v>
       </c>
       <c r="K244" s="2" t="n">
         <v>42218.51196867292</v>
       </c>
       <c r="L244" s="2" t="n">
-        <v>20.60271597427082</v>
+        <v>20.5799548091778</v>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1028.763203648032</v>
+        <v>1028.962622273183</v>
       </c>
       <c r="N244" s="2" t="n">
-        <v>0.006218902078516617</v>
+        <v>0.006220107569632602</v>
       </c>
       <c r="O244" s="2" t="n">
-        <v>25.70136806947755</v>
+        <v>25.70635010175354</v>
       </c>
     </row>
     <row r="245">
@@ -21917,28 +21917,28 @@
         <v>0</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>14.55009252608375</v>
+        <v>14.61061599889555</v>
       </c>
       <c r="I245" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>23796.57575646223</v>
+        <v>23895.5614779089</v>
       </c>
       <c r="K245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L245" s="2" t="n">
-        <v>8.464049025407933</v>
+        <v>8.488221545381789</v>
       </c>
       <c r="M245" s="2" t="n">
-        <v>8.967179705911567</v>
+        <v>9.004480146177244</v>
       </c>
       <c r="N245" s="2" t="n">
-        <v>0.04552578394078143</v>
+        <v>0.04571515583251588</v>
       </c>
       <c r="O245" s="2" t="n">
-        <v>4.722404004753398</v>
+        <v>4.734262740671199</v>
       </c>
     </row>
     <row r="246">
@@ -21974,28 +21974,28 @@
         <v>0</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>2.346839708812989</v>
+        <v>2.35660176971091</v>
       </c>
       <c r="I246" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>11262.24703764532</v>
+        <v>11309.09418319857</v>
       </c>
       <c r="K246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="n">
-        <v>4.005795289139398</v>
+        <v>4.017235459954482</v>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1.446350486924327</v>
+        <v>1.452366816663452</v>
       </c>
       <c r="N246" s="2" t="n">
-        <v>0.01074992288810206</v>
+        <v>0.01079463893815334</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>1.365507561270612</v>
+        <v>1.368936576142396</v>
       </c>
     </row>
     <row r="247">
@@ -22031,28 +22031,28 @@
         <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>32.17051207112068</v>
+        <v>32.1024629734608</v>
       </c>
       <c r="I247" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>7822.90973056083</v>
+        <v>7806.362218135087</v>
       </c>
       <c r="K247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L247" s="2" t="n">
-        <v>2.782479805432788</v>
+        <v>2.772989119016391</v>
       </c>
       <c r="M247" s="2" t="n">
-        <v>26.48337879238174</v>
+        <v>26.42735947799152</v>
       </c>
       <c r="N247" s="2" t="n">
-        <v>0.03040662307910012</v>
+        <v>0.03034230507076868</v>
       </c>
       <c r="O247" s="2" t="n">
-        <v>3.833164819582145</v>
+        <v>3.825056667415418</v>
       </c>
     </row>
     <row r="248">
@@ -22088,28 +22088,28 @@
         <v>0</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>14.68145089899588</v>
+        <v>14.6322826684658</v>
       </c>
       <c r="I248" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>6547.168742272986</v>
+        <v>6525.242251202443</v>
       </c>
       <c r="K248" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L248" s="2" t="n">
-        <v>2.328719803191357</v>
+        <v>2.317907529257987</v>
       </c>
       <c r="M248" s="2" t="n">
-        <v>152.8028075958941</v>
+        <v>152.2910704575685</v>
       </c>
       <c r="N248" s="2" t="n">
-        <v>0.0005860040640521077</v>
+        <v>0.0005840415343872194</v>
       </c>
       <c r="O248" s="2" t="n">
-        <v>2.750219562814837</v>
+        <v>2.741009067857415</v>
       </c>
     </row>
     <row r="249">
@@ -22145,28 +22145,28 @@
         <v>0</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>5.387881344303971</v>
+        <v>5.410293111752911</v>
       </c>
       <c r="I249" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>4978.587877685963</v>
+        <v>4999.297122490838</v>
       </c>
       <c r="K249" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L249" s="2" t="n">
-        <v>1.77080149284051</v>
+        <v>1.775858733686697</v>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3.320535602223153</v>
+        <v>3.334347909318896</v>
       </c>
       <c r="N249" s="2" t="n">
-        <v>0.004967066593034552</v>
+        <v>0.004987727913184851</v>
       </c>
       <c r="O249" s="2" t="n">
-        <v>0.693603221935928</v>
+        <v>0.7102727995740883</v>
       </c>
     </row>
     <row r="250">
@@ -22202,28 +22202,28 @@
         <v>0</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>9.913121614392164</v>
+        <v>9.918289065916879</v>
       </c>
       <c r="I250" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>4501.377623699416</v>
+        <v>4503.724074350353</v>
       </c>
       <c r="K250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L250" s="2" t="n">
-        <v>1.601065686037608</v>
+        <v>1.59982044187148</v>
       </c>
       <c r="M250" s="2" t="n">
-        <v>63.75584027947673</v>
+        <v>63.7890745347272</v>
       </c>
       <c r="N250" s="2" t="n">
-        <v>0.008532527232931972</v>
+        <v>0.008536975016644771</v>
       </c>
       <c r="O250" s="2" t="n">
-        <v>0.8841024218472138</v>
+        <v>0.884563281361047</v>
       </c>
     </row>
     <row r="251">
@@ -22259,28 +22259,28 @@
         <v>0</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>3.5316256818239</v>
+        <v>3.528290086937671</v>
       </c>
       <c r="I251" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>3483.469969302053</v>
+        <v>3480.179857137636</v>
       </c>
       <c r="K251" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L251" s="2" t="n">
-        <v>1.23901274286079</v>
+        <v>1.236235343223435</v>
       </c>
       <c r="M251" s="2" t="n">
-        <v>22.88323696641385</v>
+        <v>22.86162391478203</v>
       </c>
       <c r="N251" s="2" t="n">
-        <v>0.1056322432691298</v>
+        <v>0.105532474380178</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>0.00952017484147666</v>
+        <v>0.00951118310526841</v>
       </c>
     </row>
     <row r="252">
@@ -22316,28 +22316,28 @@
         <v>333.3333333333333</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>390.5272868483686</v>
+        <v>390.5454283957022</v>
       </c>
       <c r="I252" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>164874.8093390121</v>
+        <v>164882.4684303445</v>
       </c>
       <c r="K252" s="2" t="n">
         <v>140728.3732289097</v>
       </c>
       <c r="L252" s="2" t="n">
-        <v>45.0029435376573</v>
+        <v>44.97406643675875</v>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2928.255415840753</v>
+        <v>2928.391444963481</v>
       </c>
       <c r="N252" s="2" t="n">
-        <v>0.01770138514618756</v>
+        <v>0.01770220744600454</v>
       </c>
       <c r="O252" s="2" t="n">
-        <v>73.15597017573035</v>
+        <v>73.15936856181084</v>
       </c>
     </row>
     <row r="253">
@@ -22373,28 +22373,28 @@
         <v>0</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>8.241656249167219</v>
+        <v>8.278196874098557</v>
       </c>
       <c r="I253" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>46050.81315219488</v>
+        <v>46254.98637178863</v>
       </c>
       <c r="K253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L253" s="2" t="n">
-        <v>12.56967120968832</v>
+        <v>12.6167132862583</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5.283073029072408</v>
+        <v>5.306496329462996</v>
       </c>
       <c r="N253" s="2" t="n">
-        <v>0.076017386840544</v>
+        <v>0.07635442138030431</v>
       </c>
       <c r="O253" s="2" t="n">
-        <v>5.707010966624133</v>
+        <v>5.73231385974486</v>
       </c>
     </row>
     <row r="254">
@@ -22427,25 +22427,25 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>323.4085002935787</v>
+        <v>324.8444831038311</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>325.3073946621051</v>
+        <v>326.7505985769598</v>
       </c>
       <c r="I254" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>42458.30120609484</v>
+        <v>42646.66454343108</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>42210.46229932422</v>
+        <v>42397.88315628876</v>
       </c>
       <c r="L254" s="2" t="n">
-        <v>11.58908713552409</v>
+        <v>11.63249157258159</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>250.3662980248481</v>
+        <v>251.4770309112998</v>
       </c>
       <c r="N254" s="2" t="n">
         <v>0</v>
@@ -22487,28 +22487,28 @@
         <v>333.3333333333333</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>436.4818072437415</v>
+        <v>436.4851806648663</v>
       </c>
       <c r="I255" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>29589.84759335051</v>
+        <v>29590.07628333322</v>
       </c>
       <c r="K255" s="2" t="n">
         <v>22597.23628208163</v>
       </c>
       <c r="L255" s="2" t="n">
-        <v>8.076614286136142</v>
+        <v>8.071119199659394</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>9.863552446523922</v>
+        <v>9.863628678604243</v>
       </c>
       <c r="N255" s="2" t="n">
-        <v>0.03541845423980208</v>
+        <v>0.03541872797712574</v>
       </c>
       <c r="O255" s="2" t="n">
-        <v>10.50331095985067</v>
+        <v>10.50339213640943</v>
       </c>
     </row>
     <row r="256">
@@ -22544,28 +22544,28 @@
         <v>0</v>
       </c>
       <c r="H256" s="2" t="n">
-        <v>9.750313502197505</v>
+        <v>9.792673708488632</v>
       </c>
       <c r="I256" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>15946.57033887263</v>
+        <v>16015.85016346888</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L256" s="2" t="n">
-        <v>4.352651611587093</v>
+        <v>4.368553650064479</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6.009089853307903</v>
+        <v>6.035196325243464</v>
       </c>
       <c r="N256" s="2" t="n">
-        <v>0.03050775553902292</v>
+        <v>0.030640296386845</v>
       </c>
       <c r="O256" s="2" t="n">
-        <v>3.164579156306707</v>
+        <v>3.173109899894209</v>
       </c>
     </row>
     <row r="257">
@@ -22601,28 +22601,28 @@
         <v>0</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>17.9905116247485</v>
+        <v>17.98723320119034</v>
       </c>
       <c r="I257" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>13520.73671291331</v>
+        <v>13518.27281957398</v>
       </c>
       <c r="K257" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L257" s="2" t="n">
-        <v>3.690514962947666</v>
+        <v>3.687303481598417</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>289.3263075656996</v>
+        <v>289.2735834296381</v>
       </c>
       <c r="N257" s="2" t="n">
-        <v>8.845145143937456</v>
+        <v>8.843533286930825</v>
       </c>
       <c r="O257" s="2" t="n">
-        <v>0.3685988187242241</v>
+        <v>0.368531648702825</v>
       </c>
     </row>
     <row r="258">
@@ -22658,28 +22658,28 @@
         <v>0</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>146.598161471802</v>
+        <v>146.5778196812588</v>
       </c>
       <c r="I258" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>8437.447604317578</v>
+        <v>8436.276833892061</v>
       </c>
       <c r="K258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L258" s="2" t="n">
-        <v>2.303019968067372</v>
+        <v>2.301115930749397</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>7.435609889404135</v>
+        <v>7.434578132815833</v>
       </c>
       <c r="N258" s="2" t="n">
-        <v>0.04974138258735507</v>
+        <v>0.04973448053090523</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>3.527675267393096</v>
+        <v>3.527185771272043</v>
       </c>
     </row>
     <row r="259">
@@ -22715,28 +22715,28 @@
         <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>18.80452079204806</v>
+        <v>18.77100233014284</v>
       </c>
       <c r="I259" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>8385.844940675441</v>
+        <v>8370.897438035223</v>
       </c>
       <c r="K259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="n">
-        <v>2.288934906998372</v>
+        <v>2.283282759516261</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>195.7152322538388</v>
+        <v>195.3663760596758</v>
       </c>
       <c r="N259" s="2" t="n">
-        <v>0.0007505747001780448</v>
+        <v>0.0007492368245803013</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>3.522578341026636</v>
+        <v>3.516299456856304</v>
       </c>
     </row>
     <row r="260">
@@ -22772,28 +22772,28 @@
         <v>0</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>1.572665112562793</v>
+        <v>1.57949755118951</v>
       </c>
       <c r="I260" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>7547.06124097708</v>
+        <v>7579.849424760866</v>
       </c>
       <c r="K260" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L260" s="2" t="n">
-        <v>2.059987042681413</v>
+        <v>2.067513028250402</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>0.9692289348873263</v>
+        <v>0.9734397469413085</v>
       </c>
       <c r="N260" s="2" t="n">
-        <v>0.007203742388272989</v>
+        <v>0.007235039024382856</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>0.915054442996949</v>
+        <v>0.9175211516606446</v>
       </c>
     </row>
     <row r="261">
@@ -22829,28 +22829,28 @@
         <v>0</v>
       </c>
       <c r="H261" s="2" t="n">
-        <v>154.5233649100179</v>
+        <v>153.4903994507764</v>
       </c>
       <c r="I261" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>6779.590477930062</v>
+        <v>6734.269935010341</v>
       </c>
       <c r="K261" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L261" s="2" t="n">
-        <v>1.85050420200567</v>
+        <v>1.836869051897838</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>31.96355016454155</v>
+        <v>31.74987863794795</v>
       </c>
       <c r="N261" s="2" t="n">
-        <v>0.001937218935611433</v>
+        <v>0.001924268918320258</v>
       </c>
       <c r="O261" s="2" t="n">
-        <v>3.71838396303695</v>
+        <v>3.6935271253655</v>
       </c>
     </row>
     <row r="262">
@@ -22886,28 +22886,28 @@
         <v>200</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>242.8574161971897</v>
+        <v>242.8845705329081</v>
       </c>
       <c r="I262" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>102530.7873240203</v>
+        <v>102542.2514804956</v>
       </c>
       <c r="K262" s="2" t="n">
         <v>84437.02393734583</v>
       </c>
       <c r="L262" s="2" t="n">
-        <v>29.0865006935346</v>
+        <v>29.05871195694003</v>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1820.995787504683</v>
+        <v>1821.199396402983</v>
       </c>
       <c r="N262" s="2" t="n">
-        <v>0.01100797000488106</v>
+        <v>0.01100920082631436</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>45.49354294716617</v>
+        <v>45.49862966412771</v>
       </c>
     </row>
     <row r="263">
@@ -22943,28 +22943,28 @@
         <v>0</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>12.32396426014749</v>
+        <v>12.37865206696616</v>
       </c>
       <c r="I263" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>68860.98598151628</v>
+        <v>69166.55781045104</v>
       </c>
       <c r="K263" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L263" s="2" t="n">
-        <v>19.53486527104445</v>
+        <v>19.60061390742171</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7.899917349818664</v>
+        <v>7.934973371143505</v>
       </c>
       <c r="N263" s="2" t="n">
-        <v>0.1136707877943021</v>
+        <v>0.114175203902025</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>8.533842841607528</v>
+        <v>8.571711918382755</v>
       </c>
     </row>
     <row r="264">
@@ -22997,25 +22997,25 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>486.620846145423</v>
+        <v>488.7811782137155</v>
       </c>
       <c r="I264" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>63512.5262992182</v>
+        <v>63794.48739560219</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>63315.69344898634</v>
+        <v>63596.82473443313</v>
       </c>
       <c r="L264" s="2" t="n">
-        <v>18.01758465398574</v>
+        <v>18.07826146690422</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>374.5179537578493</v>
+        <v>376.1806099142044</v>
       </c>
       <c r="N264" s="2" t="n">
         <v>0</v>
@@ -23057,28 +23057,28 @@
         <v>300</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>379.848254953457</v>
+        <v>379.8532986639671</v>
       </c>
       <c r="I265" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>25750.56230555895</v>
+        <v>25750.90422731336</v>
       </c>
       <c r="K265" s="2" t="n">
         <v>20337.51265387347</v>
       </c>
       <c r="L265" s="2" t="n">
-        <v>7.305061902943921</v>
+        <v>7.297363747806717</v>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8.583755662379293</v>
+        <v>8.583869639416402</v>
       </c>
       <c r="N265" s="2" t="n">
-        <v>0.03082290673486162</v>
+        <v>0.0308233160083455</v>
       </c>
       <c r="O265" s="2" t="n">
-        <v>9.140505453197218</v>
+        <v>9.140626822883192</v>
       </c>
     </row>
     <row r="266">
@@ -23114,28 +23114,28 @@
         <v>0</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>14.40674078680686</v>
+        <v>14.46976419575465</v>
       </c>
       <c r="I266" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>23562.12497771922</v>
+        <v>23665.19932743681</v>
       </c>
       <c r="K266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L266" s="2" t="n">
-        <v>6.684233900786809</v>
+        <v>6.706310820475397</v>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8.878832445923601</v>
+        <v>8.917673589559007</v>
       </c>
       <c r="N266" s="2" t="n">
-        <v>0.04507725068931546</v>
+        <v>0.04527444463112892</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>4.67587750834549</v>
+        <v>4.688622677061513</v>
       </c>
     </row>
     <row r="267">
@@ -23171,28 +23171,28 @@
         <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>15.33803161601061</v>
+        <v>15.33312425216871</v>
       </c>
       <c r="I267" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>11527.27012438807</v>
+        <v>11523.58200390296</v>
       </c>
       <c r="K267" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L267" s="2" t="n">
-        <v>3.270119729091605</v>
+        <v>3.26558511568558</v>
       </c>
       <c r="M267" s="2" t="n">
-        <v>246.6686965523332</v>
+        <v>246.5897755360845</v>
       </c>
       <c r="N267" s="2" t="n">
-        <v>7.541037114213365</v>
+        <v>7.538624378746964</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>0.3142534494371473</v>
+        <v>0.3141529048527072</v>
       </c>
     </row>
     <row r="268">
@@ -23228,28 +23228,28 @@
         <v>0</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>2.323717962098367</v>
+        <v>2.333883247194549</v>
       </c>
       <c r="I268" s="2" t="n">
         <v>4798.899130329468</v>
       </c>
       <c r="J268" s="2" t="n">
-        <v>11151.28810744482</v>
+        <v>11200.07028525244</v>
       </c>
       <c r="K268" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="n">
-        <v>3.163459071527197</v>
+        <v>3.173907453929259</v>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1.432100621672069</v>
+        <v>1.438365457311833</v>
       </c>
       <c r="N268" s="2" t="n">
-        <v>0.010644011524285</v>
+        <v>0.01069057458119476</v>
       </c>
       <c r="O268" s="2" t="n">
-        <v>1.352054184011809</v>
+        <v>1.3557395155154</v>
       </c>
     </row>
     <row r="269">
@@ -23285,28 +23285,28 @@
         <v>0</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>17.48559188222232</v>
+        <v>17.43541401974733</v>
       </c>
       <c r="I269" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>7797.670775117873</v>
+        <v>7775.294040351642</v>
       </c>
       <c r="K269" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L269" s="2" t="n">
-        <v>2.212086362817634</v>
+        <v>2.203384718367204</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>181.9879758792969</v>
+        <v>181.4657306108907</v>
       </c>
       <c r="N269" s="2" t="n">
-        <v>0.0006979301961252089</v>
+        <v>0.0006959273674171962</v>
       </c>
       <c r="O269" s="2" t="n">
-        <v>3.275508476152933</v>
+        <v>3.266108850737957</v>
       </c>
     </row>
     <row r="270">
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>119.5793417153552</v>
+        <v>119.5488095777085</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>6882.381198731238</v>
+        <v>6880.623923544053</v>
       </c>
       <c r="K270" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>1.952431954681456</v>
+        <v>1.949850581507154</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6.065187495534568</v>
+        <v>6.063638874035152</v>
       </c>
       <c r="N270" s="2" t="n">
-        <v>0.04057378159515082</v>
+        <v>0.04056342191038639</v>
       </c>
       <c r="O270" s="2" t="n">
-        <v>2.877505979783693</v>
+        <v>2.876771267521579</v>
       </c>
     </row>
     <row r="271">
@@ -23399,28 +23399,28 @@
         <v>0</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>139.4610812111397</v>
+        <v>137.9160849971049</v>
       </c>
       <c r="I271" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>6118.74468803764</v>
+        <v>6050.959200534129</v>
       </c>
       <c r="K271" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L271" s="2" t="n">
-        <v>1.735799326788876</v>
+        <v>1.714737856179823</v>
       </c>
       <c r="M271" s="2" t="n">
-        <v>28.84787855797251</v>
+        <v>28.52829217037291</v>
       </c>
       <c r="N271" s="2" t="n">
-        <v>0.001748387031698327</v>
+        <v>0.001729017819003412</v>
       </c>
       <c r="O271" s="2" t="n">
-        <v>3.355931629791194</v>
+        <v>3.318753503696378</v>
       </c>
     </row>
   </sheetData>
